--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>90991</v>
+        <v>90997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>90997</v>
+        <v>91001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91001</v>
+        <v>91003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91003</v>
+        <v>91016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91016</v>
+        <v>91018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91018</v>
+        <v>91021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91021</v>
+        <v>91031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91031</v>
+        <v>91032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91035</v>
+        <v>91037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91037</v>
+        <v>91042</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91042</v>
+        <v>91054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91054</v>
+        <v>91055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>

--- a/artfynd/S 2250-2024 artfynd.xlsx
+++ b/artfynd/S 2250-2024 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>137075654</v>
       </c>
       <c r="B9" t="n">
-        <v>91058</v>
+        <v>91062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>137075670</v>
       </c>
       <c r="B279" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
